--- a/scripts/tests/fixtures/overview/workbook-distributor-overview.xlsx
+++ b/scripts/tests/fixtures/overview/workbook-distributor-overview.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="83">
   <si>
     <t>{{report.title}}</t>
   </si>
@@ -152,6 +152,12 @@
     <t>Amounts with no rate</t>
   </si>
   <si>
+    <t>Portfolios with no valuation on or before 2026-06-15</t>
+  </si>
+  <si>
+    <t>Portfolios with no valuation at the previous quarter end</t>
+  </si>
+  <si>
     <t>conseq:8809001</t>
   </si>
   <si>
@@ -248,7 +254,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-15T08:00:00Z</t>
+    <t>2026-10-04T10:30:21Z</t>
   </si>
   <si>
     <t>Values are each portfolio's latest valuation on or before 2026-06-15, converted into CZK at that day's rate; a total that includes an amount with no rate is left empty.</t>
@@ -348,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="34.0"/>
@@ -492,6 +498,32 @@
         <v>37</v>
       </c>
       <c r="E12" s="11"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" s="12" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="C13" s="9"/>
+      <c r="D13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" s="11"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" s="12" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="C14" s="9"/>
+      <c r="D14" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" s="11"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -567,19 +599,19 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>212440.0</v>
@@ -594,7 +626,7 @@
         <v>3.629268</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K5" s="12" t="n">
         <v>0.0</v>
@@ -605,19 +637,19 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>49</v>
       </c>
       <c r="F6" s="9" t="n">
         <v>7919.94</v>
@@ -632,7 +664,7 @@
         <v>-0.038622</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K6" s="12" t="n">
         <v>0.0</v>
@@ -723,13 +755,13 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="1" t="s">
@@ -757,13 +789,13 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="D6" s="10" t="n">
         <v>122.0</v>
@@ -801,13 +833,13 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D7" s="10" t="n">
         <v>132.0</v>
@@ -845,19 +877,19 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D8" s="10" t="n">
         <v>10.0</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F8" s="10" t="n">
         <v>9.9</v>
@@ -921,10 +953,10 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6">
@@ -932,7 +964,7 @@
         <v>36</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7">
@@ -940,7 +972,7 @@
         <v>38</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8">
@@ -953,42 +985,42 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15">
@@ -998,17 +1030,17 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
